--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6703-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6703-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E17B012-55B6-4CB6-B805-8C85CF996AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0E2B701-4F8C-4B0E-BC4E-564C29A0E8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A1B6FA43-46FD-42DC-A47A-1BF2BD5CE487}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F00703A7-29A1-4C75-8999-70E43A821D88}"/>
   </bookViews>
   <sheets>
     <sheet name="6703-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1499,25 +1499,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9F5B3C-F807-4564-A958-A9640AD4444E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{684699FD-186A-4B50-99FA-B4169F1B0358}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.25" customWidth="1"/>
+    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1545,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1671,7 +1671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>25</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="42"/>
       <c r="B8" s="16" t="s">
         <v>26</v>
@@ -1859,7 +1859,7 @@
       <c r="Q8" s="46"/>
       <c r="R8" s="46"/>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="51">
         <v>2024</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>25</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>25</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>25</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2023</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2191,7 +2191,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="51">
         <v>2022</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>25</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>25</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="39">
         <v>2021</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
         <v>2020</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2019</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
         <v>39</v>
       </c>
